--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -42,12 +42,12 @@
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>95.95</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>65.07</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="4">
@@ -533,13 +533,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2203</v>
+        <v>2102</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52.03</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2102</v>
+        <v>2203</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46.91</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44.74</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>30.76</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>29.51</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>27.13</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>21.59</v>
+        <v>8.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>42.93</v>
+        <v>429.35</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>29.02</v>
+        <v>290.16</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25.6</v>
+        <v>255.99</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24.99</v>
+        <v>249.9</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.95</v>
+        <v>209.51</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.09</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.44</v>
+        <v>124.39</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.1</v>
+        <v>110.96</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.8</v>
+        <v>88.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-05 07:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
